--- a/programme/chair-sheets/S38.xlsx
+++ b/programme/chair-sheets/S38.xlsx
@@ -46,7 +46,7 @@
     <t xml:space="preserve">Session chair</t>
   </si>
   <si>
-    <t xml:space="preserve">Dr. Ratnesh Litoriya</t>
+    <t xml:space="preserve">V. D. V. Nagalakshmi</t>
   </si>
   <si>
     <t xml:space="preserve">Co-chair</t>
@@ -58,7 +58,7 @@
     <t xml:space="preserve">Joining link</t>
   </si>
   <si>
-    <t xml:space="preserve">to be confirmed</t>
+    <t xml:space="preserve">https://meet.google.com/vgs-ruvf-jtt</t>
   </si>
   <si>
     <t xml:space="preserve">#</t>

--- a/programme/chair-sheets/S38.xlsx
+++ b/programme/chair-sheets/S38.xlsx
@@ -52,7 +52,7 @@
     <t xml:space="preserve">Co-chair</t>
   </si>
   <si>
-    <t xml:space="preserve">-</t>
+    <t xml:space="preserve">Dr. Archana B</t>
   </si>
   <si>
     <t xml:space="preserve">Joining link</t>
